--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA7B581-C6FE-46A5-85EB-1FCFFDB3B267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1997A6B-9254-4F12-85C8-4F42A9DE514E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
   <si>
     <t>Client</t>
   </si>
@@ -135,9 +135,6 @@
     <t>LegalAdvisorComp</t>
   </si>
   <si>
-    <t>LegalAdvisorHL</t>
-  </si>
-  <si>
     <t>StdUser</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>Do Not Disclose</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
     <t>Public Equity</t>
   </si>
   <si>
@@ -183,18 +177,12 @@
     <t>Cleared</t>
   </si>
   <si>
-    <t>FR</t>
-  </si>
-  <si>
     <t>Consulting</t>
   </si>
   <si>
     <t>10000</t>
   </si>
   <si>
-    <t>Africa</t>
-  </si>
-  <si>
     <t>CaoUser</t>
   </si>
   <si>
@@ -354,13 +342,25 @@
     <t>Derek Janisch</t>
   </si>
   <si>
-    <t>LA</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
     <t>9999</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>FVA</t>
+  </si>
+  <si>
+    <t>No Restrictions</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -741,6 +741,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DDF7F8-97FD-42A2-944F-A031EA0AEA0E}">
   <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -833,109 +836,99 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
         <v>36</v>
       </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" t="s">
         <v>37</v>
       </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="U2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" t="s">
         <v>103</v>
       </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC2" t="s">
         <v>104</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="AD2" t="s">
         <v>105</v>
-      </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -950,12 +943,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -973,12 +966,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -997,18 +990,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1023,54 +1016,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1088,142 +1081,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1239,12 +1232,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1263,18 +1256,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1997A6B-9254-4F12-85C8-4F42A9DE514E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B15F72C-4FA7-4197-9147-44AA70B1A7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
   <si>
     <t>Client</t>
   </si>
@@ -120,9 +120,6 @@
     <t>RecordType</t>
   </si>
   <si>
-    <t>FASJobType</t>
-  </si>
-  <si>
     <t>MarketCap</t>
   </si>
   <si>
@@ -348,19 +345,19 @@
     <t>9999</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
-    <t>Drew Koecher</t>
-  </si>
-  <si>
-    <t>FVA</t>
-  </si>
-  <si>
-    <t>No Restrictions</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>FR</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>LegalAdvisorHL</t>
+  </si>
+  <si>
+    <t>Ayati Arvind</t>
+  </si>
+  <si>
+    <t>Africa</t>
   </si>
 </sst>
 </file>
@@ -822,113 +819,123 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
         <v>101</v>
       </c>
       <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="R2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
-        <v>102</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>39</v>
       </c>
-      <c r="S2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
         <v>100</v>
       </c>
-      <c r="U2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB2" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="AC2" t="s">
         <v>104</v>
       </c>
       <c r="AD2" t="s">
-        <v>105</v>
+        <v>34</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -943,12 +950,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -966,12 +973,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -990,18 +997,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s">
         <v>97</v>
-      </c>
-      <c r="B2" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1016,54 +1023,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1081,142 +1088,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1232,12 +1239,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1256,18 +1263,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B15F72C-4FA7-4197-9147-44AA70B1A7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB176DE5-AEF6-4C48-8843-F3348DC8782C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
@@ -141,9 +141,6 @@
     <t>Creditor Advisors</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
   </si>
   <si>
     <t>Africa</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -440,9 +440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -480,7 +480,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -586,7 +586,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -728,7 +728,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -834,7 +834,7 @@
         <v>28</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>29</v>
@@ -851,91 +851,91 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC2" t="s">
         <v>103</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="U2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>104</v>
-      </c>
       <c r="AD2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AF2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -950,12 +950,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -973,12 +973,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1000,15 +1000,15 @@
         <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s">
         <v>96</v>
-      </c>
-      <c r="B2" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1023,54 +1023,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1088,142 +1088,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1239,12 +1239,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1263,18 +1263,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB176DE5-AEF6-4C48-8843-F3348DC8782C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F11BD-74F5-449D-A917-58A2B331BF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -330,9 +330,6 @@
     <t>Opportunities</t>
   </si>
   <si>
-    <t>William Peluchiwski</t>
-  </si>
-  <si>
     <t>Derek Janisch</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Eric Winthrop</t>
   </si>
 </sst>
 </file>
@@ -834,7 +834,7 @@
         <v>28</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>29</v>
@@ -851,7 +851,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -872,7 +872,7 @@
         <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L2" t="s">
         <v>35</v>
@@ -881,16 +881,16 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R2" t="s">
         <v>37</v>
@@ -899,7 +899,7 @@
         <v>37</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U2" t="s">
         <v>38</v>
@@ -914,19 +914,19 @@
         <v>41</v>
       </c>
       <c r="Y2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z2" t="s">
         <v>42</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AB2" s="4" t="s">
         <v>43</v>
       </c>
       <c r="AC2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AD2" t="s">
         <v>33</v>
@@ -935,7 +935,7 @@
         <v>33</v>
       </c>
       <c r="AF2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" t="s">
         <v>95</v>
-      </c>
-      <c r="B2" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8F11BD-74F5-449D-A917-58A2B331BF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106A5326-2C6D-4F77-A8DE-86F702B0266B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
   <si>
     <t>Client</t>
   </si>
@@ -358,6 +358,21 @@
   </si>
   <si>
     <t>Eric Winthrop</t>
+  </si>
+  <si>
+    <t>Ulrich Graebner</t>
+  </si>
+  <si>
+    <t>Lucy Gao</t>
+  </si>
+  <si>
+    <t>Luke Tweedie</t>
+  </si>
+  <si>
+    <t>Tanya Wong</t>
+  </si>
+  <si>
+    <t>Doria Chen</t>
   </si>
 </sst>
 </file>
@@ -387,12 +402,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -407,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -422,6 +443,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1080,148 +1102,164 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4D31B6-974B-4F27-AE1C-8524FC5854B9}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>82</v>
       </c>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106A5326-2C6D-4F77-A8DE-86F702B0266B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DE41D8-CCC0-4576-8D41-2829464D7477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
@@ -309,9 +309,6 @@
     <t>26</t>
   </si>
   <si>
-    <t>Joseph Julian</t>
-  </si>
-  <si>
     <t>Laura Kimmel</t>
   </si>
   <si>
@@ -360,9 +357,6 @@
     <t>Eric Winthrop</t>
   </si>
   <si>
-    <t>Ulrich Graebner</t>
-  </si>
-  <si>
     <t>Lucy Gao</t>
   </si>
   <si>
@@ -373,6 +367,12 @@
   </si>
   <si>
     <t>Doria Chen</t>
+  </si>
+  <si>
+    <t>James Santoro</t>
+  </si>
+  <si>
+    <t>Brennan Ross</t>
   </si>
 </sst>
 </file>
@@ -856,7 +856,7 @@
         <v>28</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>29</v>
@@ -873,7 +873,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -894,7 +894,7 @@
         <v>33</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L2" t="s">
         <v>35</v>
@@ -903,16 +903,16 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R2" t="s">
         <v>37</v>
@@ -921,7 +921,7 @@
         <v>37</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U2" t="s">
         <v>38</v>
@@ -936,19 +936,19 @@
         <v>41</v>
       </c>
       <c r="Y2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z2" t="s">
         <v>42</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AB2" s="4" t="s">
         <v>43</v>
       </c>
       <c r="AC2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AD2" t="s">
         <v>33</v>
@@ -957,7 +957,7 @@
         <v>33</v>
       </c>
       <c r="AF2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -972,12 +972,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -995,12 +995,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1027,10 +1027,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>60</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>66</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>68</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>69</v>
@@ -1223,15 +1223,15 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1251,7 +1251,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DE41D8-CCC0-4576-8D41-2829464D7477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF1D628-A0DB-403A-84B6-77D613BBA173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -345,9 +345,6 @@
     <t>LegalAdvisorHL</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
     <t>Africa</t>
   </si>
   <si>
@@ -373,6 +370,9 @@
   </si>
   <si>
     <t>Brennan Ross</t>
+  </si>
+  <si>
+    <t>Andy Chen</t>
   </si>
 </sst>
 </file>
@@ -759,12 +759,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DDF7F8-97FD-42A2-944F-A031EA0AEA0E}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,7 +866,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -873,7 +877,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -903,7 +907,7 @@
         <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O2" s="4" t="s">
         <v>95</v>
@@ -948,7 +952,7 @@
         <v>43</v>
       </c>
       <c r="AC2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="AD2" t="s">
         <v>33</v>
@@ -957,7 +961,7 @@
         <v>33</v>
       </c>
       <c r="AF2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -968,14 +972,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAAB1BF-28A0-4F9D-AF12-163DFEE79EC9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -988,17 +992,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81476466-7D15-422C-A40B-DB48EF57C5AD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -1011,13 +1015,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90537D08-6E7F-4E54-8CDB-35A7330A3F4E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
@@ -1025,9 +1029,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>94</v>
@@ -1041,9 +1045,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51E48BF-85F6-4333-9229-666FC33867BB}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1069,7 +1073,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1103,163 +1107,163 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4D31B6-974B-4F27-AE1C-8524FC5854B9}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>82</v>
       </c>
@@ -1273,14 +1277,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB52C45-D3D8-4909-AFE3-066895640772}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -1293,13 +1297,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F878363-A374-4264-8076-44FFB06F4C56}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="68.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>84</v>
       </c>
@@ -1307,7 +1311,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>86</v>
       </c>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF1D628-A0DB-403A-84B6-77D613BBA173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3F2947-9994-4C24-9C3C-80AECFADC197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>66</v>
@@ -1166,12 +1166,12 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>68</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>69</v>
@@ -1187,47 +1187,47 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>88</v>
@@ -1235,37 +1235,37 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1278,6 +1278,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB52C45-D3D8-4909-AFE3-066895640772}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1286,7 +1289,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3F2947-9994-4C24-9C3C-80AECFADC197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3E6782-06FC-43D6-87FD-CBE59CF62D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
     <t>Africa</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Eric Winthrop</t>
   </si>
   <si>
@@ -373,13 +367,19 @@
   </si>
   <si>
     <t>Andy Chen</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,8 +401,123 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color indexed="54"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,8 +530,88 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -424,11 +619,155 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="49"/>
+      </top>
+      <bottom style="double">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="2" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="8" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -444,9 +783,53 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{BF99A528-9FF5-46D1-ACF8-7E1E565F900D}"/>
+    <cellStyle name="20% - Accent2 2" xfId="7" xr:uid="{3A63D44C-A7F8-4530-B022-097173595E92}"/>
+    <cellStyle name="20% - Accent3 2" xfId="3" xr:uid="{20511E4B-2F7F-4784-83AF-E6CDFB4A3B12}"/>
+    <cellStyle name="20% - Accent4 2" xfId="4" xr:uid="{A7F77964-16FF-4AF2-9112-8AFE863B624C}"/>
+    <cellStyle name="20% - Accent5 2" xfId="5" xr:uid="{2C5E1BEE-A2A7-4058-AF39-B331F59EF833}"/>
+    <cellStyle name="20% - Accent6 2" xfId="6" xr:uid="{3EF98503-7FD7-4B26-9920-33D8CA8B190F}"/>
+    <cellStyle name="40% - Accent1 2" xfId="9" xr:uid="{2724DE9F-9B0B-468C-BA26-AA7ABE4F632F}"/>
+    <cellStyle name="40% - Accent2 2" xfId="7" xr:uid="{969277A9-8E37-4CA9-B349-7213C7859394}"/>
+    <cellStyle name="40% - Accent3 2" xfId="8" xr:uid="{3BEA8835-61D9-44A5-BD6E-484DCCB3DCFB}"/>
+    <cellStyle name="40% - Accent4 2" xfId="10" xr:uid="{DB66DDBB-32D8-4E64-B785-5EFC55D9E161}"/>
+    <cellStyle name="40% - Accent5 2" xfId="9" xr:uid="{94A59014-4647-4497-8594-4D3A5F810B0E}"/>
+    <cellStyle name="40% - Accent6 2" xfId="10" xr:uid="{A502FE34-F07F-4249-A647-2F07FAE6B53A}"/>
+    <cellStyle name="60% - Accent1 2" xfId="11" xr:uid="{80F6B557-3D20-4358-AF9F-642396121CBE}"/>
+    <cellStyle name="60% - Accent2 2" xfId="12" xr:uid="{293546DA-53C7-409D-A6A0-96FD98449859}"/>
+    <cellStyle name="60% - Accent3 2" xfId="13" xr:uid="{6CABEAEB-2B5C-464D-AF30-547C7B964B86}"/>
+    <cellStyle name="60% - Accent4 2" xfId="14" xr:uid="{E4C370ED-76BD-4C31-B5C3-DC3DC41DCB52}"/>
+    <cellStyle name="60% - Accent5 2" xfId="15" xr:uid="{13133BDA-B2A0-4DD8-8ACC-88016DA4CA35}"/>
+    <cellStyle name="60% - Accent6 2" xfId="20" xr:uid="{C2A870CE-317B-413A-9F59-1915FDE02777}"/>
+    <cellStyle name="Accent1 2" xfId="15" xr:uid="{015643B9-E4F2-4315-BD2F-E03AE00E4028}"/>
+    <cellStyle name="Accent2 2" xfId="16" xr:uid="{3C46A8E3-1FBC-4CE7-BDAC-F044D75154E6}"/>
+    <cellStyle name="Accent3 2" xfId="17" xr:uid="{05DD2D4C-ECD9-48BE-B4A5-560362B34DB6}"/>
+    <cellStyle name="Accent4 2" xfId="18" xr:uid="{530CABCF-0277-4A0C-A31B-0E78919EEE49}"/>
+    <cellStyle name="Accent5 2" xfId="19" xr:uid="{18A36172-7D80-4F0F-B7A6-538442D11F4F}"/>
+    <cellStyle name="Accent6 2" xfId="20" xr:uid="{AA7C4043-4F84-4764-9D3E-7EE5132634B8}"/>
+    <cellStyle name="Bad 2" xfId="21" xr:uid="{23E28C81-B23F-47AE-9203-9E4EDF64629D}"/>
+    <cellStyle name="Calculation 2" xfId="22" xr:uid="{4C34AD6D-397C-4CBE-935D-7CB7D018BAD0}"/>
+    <cellStyle name="Check Cell 2" xfId="23" xr:uid="{AC26B328-21AB-4386-B529-856C12C51021}"/>
+    <cellStyle name="Explanatory Text 2" xfId="24" xr:uid="{1D4AC857-D408-4D53-93DC-3160503D8023}"/>
+    <cellStyle name="Good 2" xfId="25" xr:uid="{3E33B8F0-243C-4325-BF80-DD1898C79AC4}"/>
+    <cellStyle name="Heading 1 2" xfId="26" xr:uid="{23F6D648-9FC5-4362-AC79-E352BFF7C1D1}"/>
+    <cellStyle name="Heading 2 2" xfId="27" xr:uid="{FE2AEA0D-E3A7-4E67-ACF7-4D36E79F4BB1}"/>
+    <cellStyle name="Heading 3 2" xfId="28" xr:uid="{808F1F5C-A9C6-42C3-926D-E6EAA11D5A56}"/>
+    <cellStyle name="Heading 4 2" xfId="29" xr:uid="{71B3FC82-E7CE-4C12-928C-42333BF1CBA2}"/>
+    <cellStyle name="Input 2" xfId="30" xr:uid="{6114B535-EB2B-4544-88D5-E4AAC6D7DEB3}"/>
+    <cellStyle name="Linked Cell 2" xfId="31" xr:uid="{4C27FB30-70C8-46F9-9E13-6069702B0EFB}"/>
+    <cellStyle name="Neutral 2" xfId="32" xr:uid="{9CE73027-5880-443C-BCAE-7020D2C260FC}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{9E094360-F413-476D-AEC2-DCD13D886B91}"/>
+    <cellStyle name="Note 2" xfId="33" xr:uid="{5E6DA4E7-C53A-48CC-B542-AD4431D29F9B}"/>
+    <cellStyle name="Output 2" xfId="34" xr:uid="{D3EE2989-D8E6-4FD4-ABE1-D9EBD71A6098}"/>
+    <cellStyle name="Title 2" xfId="35" xr:uid="{A39474E5-FB46-4CE1-B30F-7951FF201820}"/>
+    <cellStyle name="Total 2" xfId="36" xr:uid="{A3287FBB-D1CC-4E60-A1CE-512464820B57}"/>
+    <cellStyle name="Warning Text 2" xfId="37" xr:uid="{55E8F38F-F194-40C0-B810-4AC44EE2E73A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -778,190 +1161,190 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>107</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="N2" t="s">
-        <v>109</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>37</v>
       </c>
-      <c r="S2" t="s">
-        <v>37</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
         <v>96</v>
       </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>39</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>41</v>
       </c>
-      <c r="Y2" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="AA2" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="AC2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AD2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AE2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -976,12 +1359,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -999,12 +1382,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1023,18 +1406,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1049,54 +1432,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1115,157 +1498,157 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1284,12 +1667,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1308,18 +1691,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3E6782-06FC-43D6-87FD-CBE59CF62D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F81DB59-4E7C-4238-9515-2456DC3A9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -372,7 +372,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -767,7 +767,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -783,8 +783,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{BF99A528-9FF5-46D1-ACF8-7E1E565F900D}"/>
@@ -1142,16 +1140,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DDF7F8-97FD-42A2-944F-A031EA0AEA0E}">
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,7 +1160,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1249,7 +1248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1259,7 +1258,7 @@
       <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" t="s">
         <v>109</v>
       </c>
       <c r="E2" t="s">
@@ -1355,14 +1354,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCAAB1BF-28A0-4F9D-AF12-163DFEE79EC9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -1375,17 +1374,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81476466-7D15-422C-A40B-DB48EF57C5AD}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -1398,13 +1397,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90537D08-6E7F-4E54-8CDB-35A7330A3F4E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -1428,9 +1427,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51E48BF-85F6-4333-9229-666FC33867BB}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1456,7 +1455,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1490,23 +1489,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4D31B6-974B-4F27-AE1C-8524FC5854B9}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>105</v>
       </c>
@@ -1514,32 +1513,32 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1547,12 +1546,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>103</v>
       </c>
@@ -1560,7 +1559,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -1568,47 +1567,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>106</v>
       </c>
@@ -1616,37 +1615,37 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>101</v>
       </c>
@@ -1660,17 +1659,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB52C45-D3D8-4909-AFE3-066895640772}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -1683,13 +1682,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F878363-A374-4264-8076-44FFB06F4C56}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.28515625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
@@ -1697,7 +1696,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>85</v>
       </c>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F81DB59-4E7C-4238-9515-2456DC3A9F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B8050E-DA7D-49B8-902C-D382A51E0CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -279,9 +279,6 @@
     <t>Shane Soobotin</t>
   </si>
   <si>
-    <t>Shesh Bhatnagar</t>
-  </si>
-  <si>
     <t>Spencer Anderson</t>
   </si>
   <si>
@@ -373,6 +370,9 @@
   </si>
   <si>
     <t>CSDN-0000002536</t>
+  </si>
+  <si>
+    <t>Cam Chambers</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1161,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -1242,7 +1242,7 @@
         <v>27</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>28</v>
@@ -1259,7 +1259,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -1280,7 +1280,7 @@
         <v>32</v>
       </c>
       <c r="K2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
         <v>34</v>
@@ -1289,16 +1289,16 @@
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R2" t="s">
         <v>36</v>
@@ -1307,7 +1307,7 @@
         <v>36</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U2" t="s">
         <v>37</v>
@@ -1322,19 +1322,19 @@
         <v>40</v>
       </c>
       <c r="Y2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Z2" t="s">
         <v>41</v>
       </c>
       <c r="AA2" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB2" s="4" t="s">
         <v>42</v>
       </c>
       <c r="AC2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AD2" t="s">
         <v>32</v>
@@ -1343,7 +1343,7 @@
         <v>32</v>
       </c>
       <c r="AF2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1358,12 +1358,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1381,12 +1381,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>59</v>
@@ -1548,12 +1548,12 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>67</v>
@@ -1604,15 +1604,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1622,32 +1622,32 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1666,12 +1666,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1690,18 +1690,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A2BB13-D5B4-4435-AED1-BAD8F8202C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E266E7-2F89-492C-9766-0B9D358F267D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AppName" sheetId="7" r:id="rId2"/>
     <sheet name="ModuleName" sheetId="8" r:id="rId3"/>
-    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
     <sheet name="EngDealTeamMembers" sheetId="5" r:id="rId7"/>
@@ -1135,212 +1135,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DDF7F8-97FD-42A2-944F-A031EA0AEA0E}">
-  <dimension ref="A1:AF2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90537D08-6E7F-4E54-8CDB-35A7330A3F4E}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" t="s">
-        <v>105</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="R2" t="s">
-        <v>36</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1392,28 +1208,212 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90537D08-6E7F-4E54-8CDB-35A7330A3F4E}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74DDF7F8-97FD-42A2-944F-A031EA0AEA0E}">
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>105</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="R2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E266E7-2F89-492C-9766-0B9D358F267D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E65BF8-862C-405E-B5B8-3BB1D7B54377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
   <si>
     <t>Client</t>
   </si>
@@ -370,6 +370,15 @@
   </si>
   <si>
     <t>BUS - Business Services</t>
+  </si>
+  <si>
+    <t>Ryan Mahlan</t>
+  </si>
+  <si>
+    <t>Rebecca Hu</t>
+  </si>
+  <si>
+    <t>Timothy Kang</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4D31B6-974B-4F27-AE1C-8524FC5854B9}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1645,6 +1654,16 @@
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1668,7 +1687,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
